--- a/public/download/testimport.xlsx
+++ b/public/download/testimport.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">product_code</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">Website QR (SS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Batch </t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
@@ -71,15 +68,7 @@
 PRO 1 Global Home Center မှ အရည်အသွေးကောင်းမွန် သော ပစ္စည်းများကိုသာ ပစ္စည်းမှန်စျေးနှုန်းမှန်ကန်စွာရောင်းချသဖြင့် ယုံကြည်စိတ်ချစွာ ၀ယ်ယူနိုင်ပါသည်။</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Abadi"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">♦Brand: DECO
+    <t xml:space="preserve">♦Brand: DECO
 ♦Name: PVC Ceiling Gypsum Board 
 ♦Model: 239-1
 ♦Code:  2000000167503
@@ -94,17 +83,7 @@
 ♦Usage Location: Indoor
 ♦Color: Gold
 ♦Shop for variety of high quality products with reasonable price at PRO 1 Global,
-♦</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Abadi"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> leading provider for construction and home improvement products.</t>
-    </r>
+♦ leading provider for construction and home improvement products.</t>
   </si>
   <si>
     <t xml:space="preserve">Online Only</t>
@@ -118,7 +97,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -161,12 +140,6 @@
       <name val="Abadi"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Abadi"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -331,14 +304,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="47.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="88.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="88.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -363,35 +336,31 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="198.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>46266</v>
+      <c r="G2" s="5" t="n">
+        <v>46296</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H1:H1002" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G1:G1002" type="none">
       <formula1>12/30/1899</formula1>
       <formula2>12/30/1899</formula2>
     </dataValidation>
